--- a/output/pdf_financials_xlsx/RTE.xlsx
+++ b/output/pdf_financials_xlsx/RTE.xlsx
@@ -3665,28 +3665,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.094</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1101</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.36006</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.195711</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.26</v>
+        <v>1.628352</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.36</v>
+        <v>1.916981</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.386797</v>
+        <v>1.822279</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.386797</v>
+        <v>1.743079</v>
       </c>
     </row>
     <row r="93">
@@ -6085,7 +6085,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7208,7 +7212,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -7769,7 +7777,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -8206,7 +8218,11 @@
           <t>Share-based payments reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -12662,7 +12678,7 @@
         <v>-0.411632</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>0.114653</v>
+        <v>-0.114653</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>-0.284369</v>

--- a/output/pdf_financials_xlsx/RTE.xlsx
+++ b/output/pdf_financials_xlsx/RTE.xlsx
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.005583</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>-0.127219</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.127219</v>
+        <v>-0.121636</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>-0.127219</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.127219</v>
+        <v>-0.121636</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1636,31 +1636,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.119531</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.400381</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.229605</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.567051</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.757978</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.418839</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.581126</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.238404</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.18123</v>
       </c>
     </row>
     <row r="35">
@@ -1704,31 +1704,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.119531</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.400381</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.229605</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.567051</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.757978</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.418839</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.581126</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.238404</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.18123</v>
       </c>
     </row>
     <row r="37">
@@ -2112,31 +2112,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.119531</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.401898</v>
+        <v>0.001517</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.240268</v>
+        <v>0.010663</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.692308</v>
+        <v>0.125257</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.83398</v>
+        <v>0.076002</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.429464</v>
+        <v>0.010625</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.59722</v>
+        <v>0.016094</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.24086</v>
+        <v>0.002456</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.183693</v>
+        <v>0.002463</v>
       </c>
     </row>
     <row r="49">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">

--- a/output/pdf_financials_xlsx/RTE.xlsx
+++ b/output/pdf_financials_xlsx/RTE.xlsx
@@ -522,10 +522,8 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -558,10 +556,8 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
@@ -594,10 +590,8 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -630,25 +624,23 @@
       <c r="C7" s="3" t="n">
         <v>0.000203</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0.000187</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>0.047722</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.544784</v>
+        <v>0.618784</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.160989</v>
+        <v>0.293757</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.073847</v>
+        <v>0.203878</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.095772</v>
+        <v>0.130273</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>0.065914</v>
@@ -666,10 +658,8 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
@@ -700,12 +690,10 @@
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.040662</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0.055665</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0.284319</v>
@@ -738,10 +726,8 @@
       <c r="C10" s="3" t="n">
         <v>0.207732</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0.055852</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.786787</v>
@@ -774,10 +760,8 @@
       <c r="C11" s="3" t="n">
         <v>-0.207732</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-0.055852</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>-0.786787</v>
@@ -810,10 +794,8 @@
       <c r="C12" s="3" t="n">
         <v>-0.005583</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -846,10 +828,8 @@
       <c r="C13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>-0</v>
@@ -882,10 +862,8 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
@@ -918,10 +896,8 @@
       <c r="C15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
@@ -952,12 +928,10 @@
         <v>-0.127219</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>-1.143187</v>
@@ -990,10 +964,8 @@
       <c r="C17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -1128,12 +1100,10 @@
         <v>-0.127219</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-1.143187</v>
@@ -1166,10 +1136,8 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1202,10 +1170,8 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
@@ -1236,12 +1202,10 @@
         <v>-0.127219</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E23" s="3" t="n">
         <v>-1.143187</v>
@@ -1274,10 +1238,8 @@
       <c r="C24" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="E24" s="3" t="n">
         <v>-0.09</v>
@@ -1310,10 +1272,8 @@
       <c r="C25" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>-0.09</v>
@@ -1344,12 +1304,10 @@
         <v>0.636095</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3.180475</v>
-      </c>
-      <c r="D26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.369875</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>9.60615</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>12.702078</v>
@@ -1384,12 +1342,10 @@
         <v>-0.127219</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.121636</v>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.369212</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-1.143187</v>
@@ -1422,10 +1378,8 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
@@ -1456,12 +1410,10 @@
         <v>-0.127219</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.121636</v>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.369212</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-1.143187</v>
@@ -1546,10 +1498,8 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>-0</v>
@@ -3880,12 +3830,10 @@
         </is>
       </c>
       <c r="C99" s="3" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="E99" s="3" t="n">
         <v>-1.143187</v>
@@ -3920,10 +3868,8 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E100" s="3" t="n">
         <v>0</v>
@@ -3956,30 +3902,28 @@
         </is>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008921999999999999</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0.007326</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010027</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.184094</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.179623</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.088117</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.099369</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013965</v>
       </c>
     </row>
     <row r="102">
@@ -3996,10 +3940,8 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E102" s="3" t="n">
         <v>0</v>
@@ -4034,10 +3976,8 @@
       <c r="C103" s="3" t="n">
         <v>-0.001517</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>-0.009146</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>-0.114594</v>
@@ -4070,12 +4010,10 @@
         </is>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01068</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.011914</v>
       </c>
       <c r="E104" s="3" t="n">
         <v>0.358176</v>
@@ -4110,10 +4048,8 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E105" s="3" t="n">
         <v>0</v>
@@ -4146,30 +4082,28 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.002983</v>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.021119</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.010094</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.243582</v>
+        <v>0.233555</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.07212499999999999</v>
+        <v>-0.111969</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.117054</v>
+        <v>0.296677</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.00446</v>
+        <v>-0.09257700000000001</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.177843</v>
+        <v>0.277212</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>-0.04759</v>
+        <v>-0.061555</v>
       </c>
     </row>
     <row r="107">
@@ -4184,12 +4118,10 @@
         </is>
       </c>
       <c r="C107" s="3" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.094</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.0161</v>
       </c>
       <c r="E107" s="3" t="n">
         <v>0.24996</v>
@@ -4224,10 +4156,8 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E108" s="3" t="n">
         <v>0</v>
@@ -4262,10 +4192,8 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E109" s="3" t="n">
         <v>0</v>
@@ -4300,10 +4228,8 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -4318,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.005971</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.025873</v>
       </c>
     </row>
     <row r="111">
@@ -4338,16 +4264,14 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>-0.006686</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000936</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
@@ -4376,10 +4300,8 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -4414,10 +4336,8 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E113" s="3" t="n">
         <v>0</v>
@@ -4452,10 +4372,8 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>0</v>
@@ -4490,10 +4408,8 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -4528,10 +4444,8 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -4566,10 +4480,8 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E117" s="3" t="n">
         <v>0</v>
@@ -4602,12 +4514,10 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.147646</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
         <v>-0.236</v>
@@ -4639,15 +4549,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>-0.147646</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>-0.006686</v>
       </c>
       <c r="E119" s="3" t="n">
         <v>-0.236</v>
@@ -4682,10 +4588,8 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -4720,10 +4624,8 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -4758,10 +4660,8 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E122" s="3" t="n">
         <v>0</v>
@@ -4796,10 +4696,8 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
@@ -4834,10 +4732,8 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E124" s="3" t="n">
         <v>0</v>
@@ -4872,10 +4768,8 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E125" s="3" t="n">
         <v>0</v>
@@ -4910,10 +4804,8 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E126" s="3" t="n">
         <v>0</v>
@@ -4998,12 +4890,10 @@
         </is>
       </c>
       <c r="C128" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.092236</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>-0.025947</v>
@@ -5036,12 +4926,10 @@
         </is>
       </c>
       <c r="C129" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.557764</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E129" s="3" t="n">
         <v>0.874053</v>
@@ -5074,12 +4962,10 @@
         </is>
       </c>
       <c r="C130" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.119531</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>0.400381</v>
       </c>
       <c r="E130" s="3" t="n">
         <v>0.229605</v>
@@ -5114,10 +5000,8 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E131" s="3" t="n">
         <v>0</v>
@@ -5150,12 +5034,10 @@
         </is>
       </c>
       <c r="C132" s="3" t="n">
-        <v>0.119531</v>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.28085</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.170776</v>
       </c>
       <c r="E132" s="3" t="n">
         <v>0.337446</v>
@@ -5188,12 +5070,10 @@
         </is>
       </c>
       <c r="C133" s="3" t="n">
-        <v>0.119531</v>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.400381</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>0.229605</v>
       </c>
       <c r="E133" s="3" t="n">
         <v>0.567051</v>
@@ -5228,16 +5108,14 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>-0.006686</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000936</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
@@ -5263,21 +5141,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C135" s="3" t="n">
+        <v>-0.129268</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.170776</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-0.300607</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-2.695347</v>
+        <v>-2.696283</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-0.404896</v>
@@ -5303,7 +5177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M243"/>
+  <dimension ref="A1:M266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -8464,7 +8338,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -8814,7 +8692,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -9095,15 +8977,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F64" s="5" t="n">
+        <v>-0.147646</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-0.006686</v>
       </c>
       <c r="H64" s="5" t="n">
         <v>-0.236</v>
@@ -9140,7 +9018,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -9325,10 +9207,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F68" s="5" t="n">
+        <v>0.557764</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -9380,15 +9260,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F69" s="5" t="n">
+        <v>0.28085</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>-0.170776</v>
       </c>
       <c r="H69" s="5" t="n">
         <v>0.337446</v>
@@ -9435,15 +9311,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>0.119531</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.400381</v>
       </c>
       <c r="H70" s="5" t="n">
         <v>0.229605</v>
@@ -9490,15 +9362,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F71" s="5" t="n">
+        <v>0.400381</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.229605</v>
       </c>
       <c r="H71" s="5" t="n">
         <v>0.567051</v>
@@ -9671,15 +9539,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F74" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.0161</v>
       </c>
       <c r="H74" s="5" t="n">
         <v>0.24996</v>
@@ -9960,7 +9824,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -10314,25 +10182,31 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>August 31,</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F85" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -10373,27 +10247,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Cash flows from (used in) operating activities</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Net income (loss) for the year (374,795)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.001839</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -10434,12 +10312,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Write down of exploration and evaluation asset 172,646</t>
+          <t>Write down of exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -10448,10 +10326,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="5" t="n">
+        <v>0.172646</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -10497,17 +10373,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Share-based compensation 94,000</t>
+          <t>GST receivable</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInReceivables</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -10516,12 +10392,10 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.008921999999999999</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.007326</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -10562,27 +10436,29 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Decrease (increase) in</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>GST receivable (8,922)</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Prepaids</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.00025</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001517</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.009146</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -10623,17 +10499,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Decrease (increase) in</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -10642,12 +10518,10 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.001517</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.01068</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.011914</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -10688,17 +10562,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Decrease (increase) in</t>
+          <t>Change in non-cash operating working capital</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (10,680)</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10707,12 +10581,10 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.129268</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.16409</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -10753,27 +10625,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Decrease (increase) in</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Decrease (increase) in total</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
+          <t>Purchase of equipment</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.000469</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.006686</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -10814,14 +10690,14 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Expenditures on exploration and evaluation assets</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Expenditures on exploration and evaluation assets</t>
-        </is>
-      </c>
       <c r="D93" t="inlineStr">
         <is>
           <t>NetOtherInvestingChanges</t>
@@ -10833,7 +10709,7 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.147646</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -10879,12 +10755,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Issue of common shares 650,000</t>
+          <t>Issuance of common shares</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -10898,7 +10774,7 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>0.13</v>
+        <v>0.65</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -10944,22 +10820,26 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Share issue costs paid (92,236)</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.005</v>
+        <v>-0.092236</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -11003,28 +10883,20 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Cash flows from financing activities</t>
-        </is>
-      </c>
+      <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities total</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>August 31,</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.125</v>
+        <v>0.002017</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -11070,26 +10942,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cash flows from financing activities</t>
+          <t>Cash flows from (used in) operating activities</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Net change in cash during the year 280,850</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Net income (loss) for the year (374,795)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.119531</v>
+        <v>-0.127219</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -11135,26 +11003,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Cash, beginning of year                                                      119,531                _-</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cash, end of year 400,381</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Write down of exploration and evaluation asset 172,646</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F98" s="5" t="n">
-        <v>0.119531</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -11200,22 +11066,26 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Cash, beginning of year                                                      119,531                _-</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Supplemental cash flow information – See Note</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
+          <t>Share-based compensation 94,000</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F99" s="5" t="n">
-        <v>1.1e-05</v>
+        <v>0.1225</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -11256,17 +11126,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Decrease (increase) in</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Accretion expense 7 $</t>
+          <t>GST receivable (8,922)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -11275,10 +11145,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="5" t="n">
+        <v>-0.00025</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -11305,39 +11173,45 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L100" s="5" t="n">
-        <v>0.005971</v>
-      </c>
-      <c r="M100" s="5" t="n">
-        <v>0.025873</v>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Decrease (increase) in</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Amortization of equipment</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F101" s="5" t="n">
+        <v>-0.001517</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -11364,8 +11238,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L101" s="5" t="n">
-        <v>0.000284</v>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
@@ -11376,22 +11252,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Decrease (increase) in</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Consulting 9</t>
+          <t>Accounts payable and accrued liabilities (10,680)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -11399,10 +11275,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>0.0045</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -11429,8 +11303,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L102" s="5" t="n">
-        <v>0.04977</v>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
@@ -11441,17 +11317,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Decrease (increase) in</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Directors’ fees 9</t>
+          <t>Decrease (increase) in total</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -11460,10 +11336,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F103" s="5" t="n">
+        <v>-0.000469</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -11490,8 +11364,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L103" s="5" t="n">
-        <v>0.034501</v>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
@@ -11502,29 +11378,31 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenditures on exploration and evaluation assets</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Executive compensation 9</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Expenditures on exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -11551,32 +11429,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L104" s="5" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="M104" s="5" t="n">
-        <v>0.108</v>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Office and general</t>
+          <t>Issue of common shares 650,000</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -11584,10 +11466,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="5" t="n">
+        <v>0.13</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -11609,46 +11489,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K105" s="5" t="n">
-        <v>0.019869</v>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v>0.02018</v>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v>0.018646</v>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Share issue costs paid (92,236)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F106" s="5" t="n">
+        <v>-0.005</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -11660,41 +11540,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I106" s="5" t="n">
-        <v>0.158248</v>
-      </c>
-      <c r="J106" s="5" t="n">
-        <v>0.083374</v>
-      </c>
-      <c r="K106" s="5" t="n">
-        <v>0.050639</v>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v>0.063096</v>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v>0.037023</v>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Transfer agent and regulatory fees</t>
+          <t>Cash flows from financing activities total</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11702,54 +11592,64 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="5" t="n">
+        <v>0.125</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H107" s="5" t="n">
-        <v>0.006659</v>
-      </c>
-      <c r="I107" s="5" t="n">
-        <v>0.134834</v>
-      </c>
-      <c r="J107" s="5" t="n">
-        <v>0.05012</v>
-      </c>
-      <c r="K107" s="5" t="n">
-        <v>0.053978</v>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v>0.07559200000000001</v>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v>0.047268</v>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash flows from financing activities</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Net change in cash during the year 280,850</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -11757,61 +11657,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="5" t="n">
+        <v>0.119531</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>0.786787</v>
-      </c>
-      <c r="I108" s="5" t="n">
-        <v>2.979138</v>
-      </c>
-      <c r="J108" s="5" t="n">
-        <v>0.87437</v>
-      </c>
-      <c r="K108" s="5" t="n">
-        <v>0.5476569999999999</v>
-      </c>
-      <c r="L108" s="5" t="n">
-        <v>0.393394</v>
-      </c>
-      <c r="M108" s="5" t="n">
-        <v>0.23681</v>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>Cash, beginning of year                                                      119,531                _-</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Other income – flow-through premium recovery</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
+          <t>Cash, end of year 400,381</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="5" t="n">
+        <v>0.119531</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -11838,8 +11750,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L109" s="5" t="n">
-        <v>0.054771</v>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
@@ -11850,17 +11764,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>Cash, beginning of year                                                      119,531                _-</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Other income – recovery of accounts payable and accrued liabilities</t>
+          <t>Supplemental cash flow information – See Note</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -11869,10 +11783,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>1.1e-05</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -11894,11 +11806,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K110" s="5" t="n">
-        <v>0.023975</v>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v>0.027348</v>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -11914,12 +11830,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Other income – loan discount 7</t>
+          <t>Accretion expense 7 $</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -11959,12 +11875,10 @@
         </is>
       </c>
       <c r="L111" s="5" t="n">
-        <v>0.026906</v>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005971</v>
+      </c>
+      <c r="M111" s="5" t="n">
+        <v>0.025873</v>
       </c>
     </row>
     <row r="112">
@@ -11975,19 +11889,15 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES) total</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Amortization of equipment</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -12018,11 +11928,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K112" s="5" t="n">
-        <v>0.433004</v>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L112" s="5" t="n">
-        <v>0.109025</v>
+        <v>0.000284</v>
       </c>
       <c r="M112" t="inlineStr">
         <is>
@@ -12038,17 +11950,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Consulting 9</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -12081,14 +11993,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K113" s="5" t="n">
-        <v>-0.114653</v>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L113" s="5" t="n">
-        <v>-0.284369</v>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v>-0.23681</v>
+        <v>0.04977</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -12099,17 +12015,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Directors’ fees 9</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -12142,14 +12058,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K114" s="5" t="n">
-        <v>-2e-08</v>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L114" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.034501</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -12160,19 +12080,15 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
+          <t>Executive compensation 9</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -12203,14 +12119,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K115" s="5" t="n">
-        <v>7.298398</v>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L115" s="5" t="n">
-        <v>8.897697000000001</v>
+        <v>0.144</v>
       </c>
       <c r="M115" s="5" t="n">
-        <v>16.71807</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="116">
@@ -12221,15 +12139,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>August 31, 2023 7,606,343 $ 16,958,652 $ 1,556,981 $ 360,000 $</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -12261,13 +12183,13 @@
         </is>
       </c>
       <c r="K116" s="5" t="n">
-        <v>14.294599</v>
+        <v>0.019869</v>
       </c>
       <c r="L116" s="5" t="n">
-        <v>14.294599</v>
+        <v>0.02018</v>
       </c>
       <c r="M116" s="5" t="n">
-        <v>-4.581034</v>
+        <v>0.018646</v>
       </c>
     </row>
     <row r="117">
@@ -12278,24 +12200,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Private placement of flow-through units 5,609,996 871,499 - -</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F117" s="5" t="n">
+        <v>0.016272</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -12307,26 +12231,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I117" s="5" t="n">
+        <v>0.158248</v>
+      </c>
+      <c r="J117" s="5" t="n">
+        <v>0.083374</v>
       </c>
       <c r="K117" s="5" t="n">
-        <v>0.871499</v>
+        <v>0.050639</v>
       </c>
       <c r="L117" s="5" t="n">
-        <v>0.871499</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.063096</v>
+      </c>
+      <c r="M117" s="5" t="n">
+        <v>0.037023</v>
       </c>
     </row>
     <row r="118">
@@ -12337,15 +12255,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Private placement of common units 3,279,550 505,995 - -</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>Transfer agent and regulatory fees</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -12361,31 +12283,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H118" s="5" t="n">
+        <v>0.006659</v>
+      </c>
+      <c r="I118" s="5" t="n">
+        <v>0.134834</v>
+      </c>
+      <c r="J118" s="5" t="n">
+        <v>0.05012</v>
       </c>
       <c r="K118" s="5" t="n">
-        <v>0.505995</v>
+        <v>0.053978</v>
       </c>
       <c r="L118" s="5" t="n">
-        <v>0.505995</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.07559200000000001</v>
+      </c>
+      <c r="M118" s="5" t="n">
+        <v>0.047268</v>
       </c>
     </row>
     <row r="119">
@@ -12396,15 +12310,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (63,590) - -</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -12420,31 +12338,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H119" s="5" t="n">
+        <v>0.786787</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>2.979138</v>
+      </c>
+      <c r="J119" s="5" t="n">
+        <v>0.87437</v>
       </c>
       <c r="K119" s="5" t="n">
-        <v>-0.06358999999999999</v>
+        <v>0.5476569999999999</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>-0.06358999999999999</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.393394</v>
+      </c>
+      <c r="M119" s="5" t="n">
+        <v>0.23681</v>
       </c>
     </row>
     <row r="120">
@@ -12455,12 +12365,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Restricted share units exercised 120,000 156,000 (156,000) -</t>
+          <t>Other income – flow-through premium recovery</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -12499,10 +12409,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L120" s="5" t="n">
+        <v>0.054771</v>
       </c>
       <c r="M120" t="inlineStr">
         <is>
@@ -12518,12 +12426,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Restricted share units issued for services - - 34,501 -</t>
+          <t>Other income – recovery of accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -12558,10 +12466,10 @@
         </is>
       </c>
       <c r="K121" s="5" t="n">
-        <v>0.034501</v>
+        <v>0.023975</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>0.034501</v>
+        <v>0.027348</v>
       </c>
       <c r="M121" t="inlineStr">
         <is>
@@ -12577,12 +12485,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Shareholder loan discount (Note 7) - - - 26,797</t>
+          <t>Other income – loan discount 7</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -12622,7 +12530,7 @@
         </is>
       </c>
       <c r="L122" s="5" t="n">
-        <v>0.026797</v>
+        <v>0.026906</v>
       </c>
       <c r="M122" t="inlineStr">
         <is>
@@ -12638,17 +12546,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - - -</t>
+          <t>OTHER INCOME AND (EXPENSES) total</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -12671,20 +12579,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I123" s="5" t="n">
-        <v>-2.217425</v>
-      </c>
-      <c r="J123" s="5" t="n">
-        <v>-0.411632</v>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K123" s="5" t="n">
-        <v>-0.114653</v>
+        <v>0.433004</v>
       </c>
       <c r="L123" s="5" t="n">
-        <v>-0.284369</v>
-      </c>
-      <c r="M123" s="5" t="n">
-        <v>-0.284369</v>
+        <v>0.109025</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -12695,15 +12609,19 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>August 31, 2024 16,615,889 $ 18,428,556 $ 1,435,482 $ 386,797 $</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -12735,13 +12653,13 @@
         </is>
       </c>
       <c r="K124" s="5" t="n">
-        <v>15.385432</v>
+        <v>-0.114653</v>
       </c>
       <c r="L124" s="5" t="n">
-        <v>15.385432</v>
+        <v>-0.284369</v>
       </c>
       <c r="M124" s="5" t="n">
-        <v>-4.865403</v>
+        <v>-0.23681</v>
       </c>
     </row>
     <row r="125">
@@ -12752,15 +12670,19 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Issuance of shares upon exercise of RSUs 144,000 79,200 (79,200) -</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -12791,20 +12713,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K125" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="M125" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="126">
@@ -12815,15 +12731,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>August 31, 2025 16,759,889 $ 18,507,756 $ 1,356,282 $ 386,797 $</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -12854,16 +12774,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K126" s="5" t="n">
+        <v>7.298398</v>
       </c>
       <c r="L126" s="5" t="n">
-        <v>15.148622</v>
+        <v>8.897697000000001</v>
       </c>
       <c r="M126" s="5" t="n">
-        <v>-5.102213</v>
+        <v>16.71807</v>
       </c>
     </row>
     <row r="127">
@@ -12874,12 +12792,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Accretion expense 9 $</t>
+          <t>August 31, 2023 7,606,343 $ 16,958,652 $ 1,556,981 $ 360,000 $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -12913,18 +12831,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K127" s="5" t="n">
+        <v>14.294599</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>0.005971</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14.294599</v>
+      </c>
+      <c r="M127" s="5" t="n">
+        <v>-4.581034</v>
       </c>
     </row>
     <row r="128">
@@ -12935,12 +12849,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Advertising and marketing</t>
+          <t>Private placement of flow-through units 5,609,996 871,499 - -</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -12964,8 +12878,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I128" s="5" t="n">
-        <v>0.772085</v>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -12973,12 +12889,10 @@
         </is>
       </c>
       <c r="K128" s="5" t="n">
-        <v>0.016117</v>
-      </c>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.871499</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>0.871499</v>
       </c>
       <c r="M128" t="inlineStr">
         <is>
@@ -12994,12 +12908,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Amortization of equipment 7</t>
+          <t>Private placement of common units 3,279,550 505,995 - -</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -13034,10 +12948,10 @@
         </is>
       </c>
       <c r="K129" s="5" t="n">
-        <v>0.000348</v>
+        <v>0.505995</v>
       </c>
       <c r="L129" s="5" t="n">
-        <v>0.000284</v>
+        <v>0.505995</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -13053,19 +12967,15 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Consulting 11</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Share issuance costs - cash - (63,590) - -</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -13097,10 +13007,10 @@
         </is>
       </c>
       <c r="K130" s="5" t="n">
-        <v>0.05404</v>
+        <v>-0.06358999999999999</v>
       </c>
       <c r="L130" s="5" t="n">
-        <v>0.04977</v>
+        <v>-0.06358999999999999</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -13116,12 +13026,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Directors’ fees 11</t>
+          <t>Restricted share units exercised 120,000 156,000 (156,000) -</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -13155,11 +13065,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K131" s="5" t="n">
-        <v>0.130031</v>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v>0.034501</v>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -13175,12 +13089,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Executive compensation 11</t>
+          <t>Restricted share units issued for services - - 34,501 -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -13215,10 +13129,10 @@
         </is>
       </c>
       <c r="K132" s="5" t="n">
-        <v>0.144</v>
+        <v>0.034501</v>
       </c>
       <c r="L132" s="5" t="n">
-        <v>0.144</v>
+        <v>0.034501</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -13234,12 +13148,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Share-based compensation 10</t>
+          <t>Shareholder loan discount (Note 7) - - - 26,797</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -13273,13 +13187,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K133" s="5" t="n">
-        <v>0.054787</v>
-      </c>
-      <c r="L133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>0.026797</v>
       </c>
       <c r="M133" t="inlineStr">
         <is>
@@ -13295,15 +13209,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Travel, meals and related costs</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year - - - -</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -13319,27 +13237,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H134" s="5" t="n">
-        <v>0.005588</v>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I134" s="5" t="n">
-        <v>0.045633</v>
+        <v>-2.217425</v>
       </c>
       <c r="J134" s="5" t="n">
-        <v>0.010854</v>
+        <v>-0.411632</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.023848</v>
-      </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.114653</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>-0.284369</v>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>-0.284369</v>
       </c>
     </row>
     <row r="135">
@@ -13350,12 +13266,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Other income – flow-through premium recovery 10</t>
+          <t>August 31, 2024 16,615,889 $ 18,428,556 $ 1,435,482 $ 386,797 $</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -13390,15 +13306,13 @@
         </is>
       </c>
       <c r="K135" s="5" t="n">
-        <v>0.410042</v>
+        <v>15.385432</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>0.054771</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>15.385432</v>
+      </c>
+      <c r="M135" s="5" t="n">
+        <v>-4.865403</v>
       </c>
     </row>
     <row r="136">
@@ -13409,12 +13323,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Other income – loan discount 9</t>
+          <t>Issuance of shares upon exercise of RSUs 144,000 79,200 (79,200) -</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -13453,8 +13367,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L136" s="5" t="n">
-        <v>0.026906</v>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -13470,19 +13386,15 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>OTHER INCOME AND (EXPENSES)</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>August 31, 2025 16,759,889 $ 18,507,756 $ 1,356,282 $ 386,797 $</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -13513,18 +13425,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K137" s="5" t="n">
-        <v>-0.001013</v>
-      </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>15.148622</v>
+      </c>
+      <c r="M137" s="5" t="n">
+        <v>-5.102213</v>
       </c>
     </row>
     <row r="138">
@@ -13535,12 +13445,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>August 31, 2022 6,669,677 $ 16,446,104 $ 1,368,352 $ 260,000 $</t>
+          <t>Accretion expense 9 $</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -13574,11 +13484,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K138" s="5" t="n">
-        <v>13.608075</v>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L138" s="5" t="n">
-        <v>-4.466381</v>
+        <v>0.005971</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -13594,12 +13506,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Private placement of flow-through shares 936,666 562,000 - -</t>
+          <t>Advertising and marketing</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -13623,10 +13535,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I139" s="5" t="n">
+        <v>0.772085</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -13634,7 +13544,7 @@
         </is>
       </c>
       <c r="K139" s="5" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.016117</v>
       </c>
       <c r="L139" t="inlineStr">
         <is>
@@ -13655,12 +13565,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (49,452) - -</t>
+          <t>Amortization of equipment 7</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -13689,16 +13599,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J140" s="5" t="n">
-        <v>-0.049452</v>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K140" s="5" t="n">
-        <v>-0.049452</v>
-      </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000348</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>0.000284</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -13714,15 +13624,19 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Restricted share units issued for services - - 133,842 -</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
+          <t>Consulting 11</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -13748,16 +13662,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J141" s="5" t="n">
-        <v>0.133842</v>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0.133842</v>
-      </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.05404</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>0.04977</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -13773,15 +13687,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Shareholder contribution - - - 100,000</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
+          <t>Directors’ fees 11</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -13807,16 +13725,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J142" s="5" t="n">
-        <v>0.1</v>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.130031</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>0.034501</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -13832,12 +13750,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 54,787 -</t>
+          <t>Executive compensation 11</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -13866,16 +13784,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J143" s="5" t="n">
-        <v>0.054787</v>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K143" s="5" t="n">
-        <v>0.054787</v>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.144</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>0.144</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -13891,12 +13809,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Shareholder loan discount (Note 9) - - - 26,797</t>
+          <t>Share-based compensation 10</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -13931,7 +13849,7 @@
         </is>
       </c>
       <c r="K144" s="5" t="n">
-        <v>0.026797</v>
+        <v>0.054787</v>
       </c>
       <c r="L144" t="inlineStr">
         <is>
@@ -13957,7 +13875,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Advertising and marketing $</t>
+          <t>Travel, meals and related costs</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -13966,29 +13884,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F145" s="5" t="n">
+        <v>0.000975</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.033166</v>
+      </c>
+      <c r="H145" s="5" t="n">
+        <v>0.005588</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>0.772085</v>
+        <v>0.045633</v>
       </c>
       <c r="J145" s="5" t="n">
-        <v>0.10574</v>
+        <v>0.010854</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>0.016117</v>
+        <v>0.023848</v>
       </c>
       <c r="L145" t="inlineStr">
         <is>
@@ -14009,12 +13921,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Amortization of equipment (Note 6)</t>
+          <t>Other income – flow-through premium recovery 10</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -14033,22 +13945,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H146" s="5" t="n">
-        <v>0.002665</v>
-      </c>
-      <c r="I146" s="5" t="n">
-        <v>0.001714</v>
-      </c>
-      <c r="J146" s="5" t="n">
-        <v>0.000772</v>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K146" s="5" t="n">
-        <v>0.000348</v>
-      </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.410042</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>0.054771</v>
       </c>
       <c r="M146" t="inlineStr">
         <is>
@@ -14064,19 +13980,15 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Consulting (Note 8)</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Other income – loan discount 9</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -14092,22 +14004,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H147" s="5" t="n">
-        <v>0.284319</v>
-      </c>
-      <c r="I147" s="5" t="n">
-        <v>0.581811</v>
-      </c>
-      <c r="J147" s="5" t="n">
-        <v>0.192689</v>
-      </c>
-      <c r="K147" s="5" t="n">
-        <v>0.05404</v>
-      </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>0.026906</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -14123,15 +14041,19 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME AND (EXPENSES)</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Directors’ fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -14152,14 +14074,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I148" s="5" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="J148" s="5" t="n">
-        <v>0.132768</v>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K148" s="5" t="n">
-        <v>0.130031</v>
+        <v>-0.001013</v>
       </c>
       <c r="L148" t="inlineStr">
         <is>
@@ -14180,12 +14106,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Executive compensation (Note 8)</t>
+          <t>August 31, 2022 6,669,677 $ 16,446,104 $ 1,368,352 $ 260,000 $</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -14204,22 +14130,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H149" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="I149" s="5" t="n">
-        <v>0.406197</v>
-      </c>
-      <c r="J149" s="5" t="n">
-        <v>0.134001</v>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K149" s="5" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.608075</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>-4.466381</v>
       </c>
       <c r="M149" t="inlineStr">
         <is>
@@ -14235,19 +14165,15 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Private placement of flow-through shares 936,666 562,000 - -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
           <t>-</t>
@@ -14268,16 +14194,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I150" s="5" t="n">
-        <v>0.2455</v>
-      </c>
-      <c r="J150" s="5" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>0.5620000000000001</v>
       </c>
       <c r="L150" t="inlineStr">
         <is>
@@ -14298,19 +14226,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Office and general (Note 8)</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Share issuance costs - cash - (49,452) - -</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
           <t>-</t>
@@ -14326,17 +14250,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H151" s="5" t="n">
-        <v>0.017063</v>
-      </c>
-      <c r="I151" s="5" t="n">
-        <v>0.07445</v>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J151" s="5" t="n">
-        <v>0.029869</v>
+        <v>-0.049452</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>0.019869</v>
+        <v>-0.049452</v>
       </c>
       <c r="L151" t="inlineStr">
         <is>
@@ -14357,19 +14285,15 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Rent (Note 8)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Restricted share units issued for services - - 133,842 -</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
@@ -14385,19 +14309,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H152" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="I152" s="5" t="n">
-        <v>0.09</v>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J152" s="5" t="n">
-        <v>0.0375</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.133842</v>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>0.133842</v>
       </c>
       <c r="L152" t="inlineStr">
         <is>
@@ -14418,12 +14344,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 7, 8)</t>
+          <t>Shareholder contribution - - - 100,000</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -14442,17 +14368,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H153" s="5" t="n">
-        <v>0.24996</v>
-      </c>
-      <c r="I153" s="5" t="n">
-        <v>0.394666</v>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J153" s="5" t="n">
-        <v>0.053183</v>
+        <v>0.1</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>0.054787</v>
+        <v>0.1</v>
       </c>
       <c r="L153" t="inlineStr">
         <is>
@@ -14473,12 +14403,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Other income – flow-through premium recovery (Note 7)</t>
+          <t>Share-based compensation - - 54,787 -</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -14508,10 +14438,10 @@
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>0.463354</v>
+        <v>0.054787</v>
       </c>
       <c r="K154" s="5" t="n">
-        <v>0.410042</v>
+        <v>0.054787</v>
       </c>
       <c r="L154" t="inlineStr">
         <is>
@@ -14532,19 +14462,15 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Other income – recovery of accrued liabilities                                           23,975</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Shareholder loan discount (Note 9) - - - 26,797</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -14570,11 +14496,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J155" s="5" t="n">
-        <v>-0.000616</v>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K155" s="5" t="n">
-        <v>-0.001013</v>
+        <v>0.026797</v>
       </c>
       <c r="L155" t="inlineStr">
         <is>
@@ -14595,19 +14523,15 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Other income – recovery of accrued liabilities                                           23,975</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Advertising and marketing $</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
@@ -14628,16 +14552,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I156" s="5" t="n">
+        <v>0.772085</v>
       </c>
       <c r="J156" s="5" t="n">
-        <v>-0.411632</v>
+        <v>0.10574</v>
       </c>
       <c r="K156" s="5" t="n">
-        <v>-0.114653</v>
+        <v>0.016117</v>
       </c>
       <c r="L156" t="inlineStr">
         <is>
@@ -14658,19 +14580,15 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Other income – recovery of accrued liabilities                                           23,975</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Amortization of equipment (Note 6)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -14686,21 +14604,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H157" s="5" t="n">
+        <v>0.002665</v>
+      </c>
+      <c r="I157" s="5" t="n">
+        <v>0.001714</v>
       </c>
       <c r="J157" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.000772</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>0</v>
+        <v>0.000348</v>
       </c>
       <c r="L157" t="inlineStr">
         <is>
@@ -14721,17 +14635,17 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Consulting (Note 8)</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -14750,16 +14664,16 @@
         </is>
       </c>
       <c r="H158" s="5" t="n">
-        <v>12.842131</v>
+        <v>0.284319</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>51.791587</v>
+        <v>0.581811</v>
       </c>
       <c r="J158" s="5" t="n">
-        <v>66.357039</v>
+        <v>0.192689</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>72.98398</v>
+        <v>0.05404</v>
       </c>
       <c r="L158" t="inlineStr">
         <is>
@@ -14780,15 +14694,19 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>August 31, 2021 62,696,765 $ 15,846,104 $ 1,195,711 $ - $</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Directors’ fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -14810,13 +14728,13 @@
         </is>
       </c>
       <c r="I159" s="5" t="n">
-        <v>12.987066</v>
+        <v>0.074</v>
       </c>
       <c r="J159" s="5" t="n">
-        <v>12.987066</v>
+        <v>0.132768</v>
       </c>
       <c r="K159" s="5" t="n">
-        <v>-4.054749</v>
+        <v>0.130031</v>
       </c>
       <c r="L159" t="inlineStr">
         <is>
@@ -14837,12 +14755,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 4,000,000 600,000 - -</t>
+          <t>Executive compensation (Note 8)</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
@@ -14861,21 +14779,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H160" s="5" t="n">
+        <v>0.0375</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>0.6</v>
+        <v>0.406197</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.134001</v>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>0.144</v>
       </c>
       <c r="L160" t="inlineStr">
         <is>
@@ -14896,15 +14810,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Restricted share units issued for services - - 119,458 -</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Management fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
           <t>-</t>
@@ -14926,10 +14844,10 @@
         </is>
       </c>
       <c r="I161" s="5" t="n">
-        <v>0.119458</v>
+        <v>0.2455</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>0.119458</v>
+        <v>0.0435</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
@@ -14955,15 +14873,19 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Shareholder contribution - - - 260,000</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Office and general (Note 8)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -14979,21 +14901,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H162" s="5" t="n">
+        <v>0.017063</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>0.26</v>
+        <v>0.07445</v>
       </c>
       <c r="J162" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.029869</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>0.019869</v>
       </c>
       <c r="L162" t="inlineStr">
         <is>
@@ -15014,15 +14932,19 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 53,183 -</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
+          <t>Rent (Note 8)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
@@ -15038,18 +14960,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H163" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.09</v>
       </c>
       <c r="J163" s="5" t="n">
-        <v>0.053183</v>
+        <v>0.0375</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -15075,12 +14993,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>August 31, 2022 66,696,765 $ 16,446,104 $ 1,368,352 $ 260,000 $</t>
+          <t>Share-based compensation (Note 7, 8)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr"/>
@@ -15099,19 +15017,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H164" s="5" t="n">
+        <v>0.24996</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>13.608075</v>
+        <v>0.394666</v>
       </c>
       <c r="J164" s="5" t="n">
-        <v>13.608075</v>
+        <v>0.053183</v>
       </c>
       <c r="K164" s="5" t="n">
-        <v>-4.466381</v>
+        <v>0.054787</v>
       </c>
       <c r="L164" t="inlineStr">
         <is>
@@ -15132,12 +15048,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Private placement of flow-through shares 9,366,667 562,000 - -</t>
+          <t>Other income – flow-through premium recovery (Note 7)</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
@@ -15167,12 +15083,10 @@
         </is>
       </c>
       <c r="J165" s="5" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.463354</v>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>0.410042</v>
       </c>
       <c r="L165" t="inlineStr">
         <is>
@@ -15193,15 +15107,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>Other income – recovery of accrued liabilities                                           23,975</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>August 31, 2023 76,063,432 $ 16,958,652 $ 1,556,981 $ 360,000 $</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -15228,10 +15146,10 @@
         </is>
       </c>
       <c r="J166" s="5" t="n">
-        <v>14.294599</v>
+        <v>-0.000616</v>
       </c>
       <c r="K166" s="5" t="n">
-        <v>-4.581034</v>
+        <v>-0.001013</v>
       </c>
       <c r="L166" t="inlineStr">
         <is>
@@ -15252,17 +15170,17 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income – recovery of accrued liabilities                                           23,975</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Other income (Note 7)</t>
+          <t>Loss and comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -15285,16 +15203,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I167" s="5" t="n">
-        <v>0.762333</v>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J167" s="5" t="n">
-        <v>0.463354</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.411632</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>-0.114653</v>
       </c>
       <c r="L167" t="inlineStr">
         <is>
@@ -15315,17 +15233,17 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Other income – recovery of accrued liabilities                                           23,975</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
+          <t>Basic and diluted loss per common share $</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -15348,16 +15266,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I168" s="5" t="n">
-        <v>-0.00062</v>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J168" s="5" t="n">
-        <v>-0.000616</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="L168" t="inlineStr">
         <is>
@@ -15378,17 +15296,17 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SharesOutstanding</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -15407,18 +15325,16 @@
         </is>
       </c>
       <c r="H169" s="5" t="n">
-        <v>-1.143187</v>
+        <v>12.842131</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>-2.217425</v>
+        <v>51.791587</v>
       </c>
       <c r="J169" s="5" t="n">
-        <v>-0.411632</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>66.357039</v>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>72.98398</v>
       </c>
       <c r="L169" t="inlineStr">
         <is>
@@ -15439,19 +15355,15 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>August 31, 2021 62,696,765 $ 15,846,104 $ 1,195,711 $ - $</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>
@@ -15467,19 +15379,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H170" s="5" t="n">
-        <v>-9e-08</v>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I170" s="5" t="n">
-        <v>-4e-08</v>
+        <v>12.987066</v>
       </c>
       <c r="J170" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>12.987066</v>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>-4.054749</v>
       </c>
       <c r="L170" t="inlineStr">
         <is>
@@ -15505,7 +15417,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>August 31, 2020 25,730,000 $ 2,285,317 $ 360,060 $ - $</t>
+          <t>Shares issued for exploration and evaluation assets 4,000,000 600,000 - -</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -15530,10 +15442,10 @@
         </is>
       </c>
       <c r="I171" s="5" t="n">
-        <v>0.808053</v>
+        <v>0.6</v>
       </c>
       <c r="J171" s="5" t="n">
-        <v>-1.837324</v>
+        <v>0.6</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
@@ -15564,7 +15476,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Private placement 10,510,000 3,153,000 - -</t>
+          <t>Restricted share units issued for services - - 119,458 -</t>
         </is>
       </c>
       <c r="D172" t="inlineStr"/>
@@ -15589,12 +15501,10 @@
         </is>
       </c>
       <c r="I172" s="5" t="n">
-        <v>3.153</v>
-      </c>
-      <c r="J172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.119458</v>
+      </c>
+      <c r="J172" s="5" t="n">
+        <v>0.119458</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
@@ -15625,7 +15535,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (277,904) - -</t>
+          <t>Shareholder contribution - - - 260,000</t>
         </is>
       </c>
       <c r="D173" t="inlineStr"/>
@@ -15650,12 +15560,10 @@
         </is>
       </c>
       <c r="I173" s="5" t="n">
-        <v>-0.277904</v>
-      </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.26</v>
+      </c>
+      <c r="J173" s="5" t="n">
+        <v>0.26</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
@@ -15686,7 +15594,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Share issuance costs - warrants - (270,529) 270,529 -</t>
+          <t>Share-based compensation - - 53,183 -</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -15715,10 +15623,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J174" s="5" t="n">
+        <v>0.053183</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -15749,7 +15655,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Private placement - flow through shares 6,666,666 2,000,000 - -</t>
+          <t>August 31, 2022 66,696,765 $ 16,446,104 $ 1,368,352 $ 260,000 $</t>
         </is>
       </c>
       <c r="D175" t="inlineStr"/>
@@ -15774,17 +15680,13 @@
         </is>
       </c>
       <c r="I175" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="J175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>13.608075</v>
+      </c>
+      <c r="J175" s="5" t="n">
+        <v>13.608075</v>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>-4.466381</v>
       </c>
       <c r="L175" t="inlineStr">
         <is>
@@ -15810,7 +15712,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (422,304) - -</t>
+          <t>Private placement of flow-through shares 9,366,667 562,000 - -</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
@@ -15834,13 +15736,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I176" s="5" t="n">
-        <v>-0.422304</v>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" s="5" t="n">
+        <v>0.5620000000000001</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
@@ -15871,7 +15773,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Share issuance costs - warrants - (216,127) 216,127 -</t>
+          <t>August 31, 2023 76,063,432 $ 16,958,652 $ 1,556,981 $ 360,000 $</t>
         </is>
       </c>
       <c r="D177" t="inlineStr"/>
@@ -15900,15 +15802,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J177" s="5" t="n">
+        <v>14.294599</v>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>-4.581034</v>
       </c>
       <c r="L177" t="inlineStr">
         <is>
@@ -15929,15 +15827,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 13,000,000 8,060,000 - -</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
+          <t>Other income (Note 7)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -15959,12 +15861,10 @@
         </is>
       </c>
       <c r="I178" s="5" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="J178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.762333</v>
+      </c>
+      <c r="J178" s="5" t="n">
+        <v>0.463354</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
@@ -15990,15 +15890,19 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Shares issued as finder’s fee 625,000 468,750 - -</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
+          <t>Loss on foreign exchange</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -16020,12 +15924,10 @@
         </is>
       </c>
       <c r="I179" s="5" t="n">
-        <v>0.46875</v>
-      </c>
-      <c r="J179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.00062</v>
+      </c>
+      <c r="J179" s="5" t="n">
+        <v>-0.000616</v>
       </c>
       <c r="K179" t="inlineStr">
         <is>
@@ -16051,15 +15953,19 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Stock option exercises 225,000 30,000 - -</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -16075,18 +15981,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H180" s="5" t="n">
+        <v>-1.143187</v>
       </c>
       <c r="I180" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.217425</v>
+      </c>
+      <c r="J180" s="5" t="n">
+        <v>-0.411632</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
@@ -16112,44 +16014,38 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Fair value of stock options exercised - 22,100 (22,100) -</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F181" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H181" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="I181" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="J181" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
@@ -16180,7 +16076,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Warrants exercised 5,940,099 990,230 - -</t>
+          <t>August 31, 2020 25,730,000 $ 2,285,317 $ 360,060 $ - $</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -16205,12 +16101,10 @@
         </is>
       </c>
       <c r="I182" s="5" t="n">
-        <v>0.9902300000000001</v>
-      </c>
-      <c r="J182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.808053</v>
+      </c>
+      <c r="J182" s="5" t="n">
+        <v>-1.837324</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
@@ -16241,7 +16135,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Fair value of warrants exercised - 23,571 (23,571) -</t>
+          <t>Private placement 10,510,000 3,153,000 - -</t>
         </is>
       </c>
       <c r="D183" t="inlineStr"/>
@@ -16265,10 +16159,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I183" s="5" t="n">
+        <v>3.153</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -16304,7 +16196,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 394,666 -</t>
+          <t>Share issuance costs - cash - (277,904) - -</t>
         </is>
       </c>
       <c r="D184" t="inlineStr"/>
@@ -16329,7 +16221,7 @@
         </is>
       </c>
       <c r="I184" s="5" t="n">
-        <v>0.394666</v>
+        <v>-0.277904</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -16365,7 +16257,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 53,183</t>
+          <t>Share issuance costs - warrants - (270,529) 270,529 -</t>
         </is>
       </c>
       <c r="D185" t="inlineStr"/>
@@ -16389,8 +16281,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I185" s="5" t="n">
-        <v>0.053183</v>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -16426,14 +16320,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Private placement - flow through shares 6,666,666 2,000,000 - -</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -16455,10 +16345,12 @@
         </is>
       </c>
       <c r="I186" s="5" t="n">
-        <v>-0.411632</v>
-      </c>
-      <c r="J186" s="5" t="n">
-        <v>-0.411632</v>
+        <v>2</v>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -16484,12 +16376,12 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Accounting and administrative (Note 8) $</t>
+          <t>Share issuance costs - cash - (422,304) - -</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -16508,11 +16400,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H187" s="5" t="n">
-        <v>0.03485</v>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I187" s="5" t="n">
-        <v>0.004113</v>
+        <v>-0.422304</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -16543,12 +16437,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Share issuance costs - warrants - (216,127) 216,127 -</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -16567,11 +16461,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H188" s="5" t="n">
-        <v>0.01164</v>
-      </c>
-      <c r="I188" s="5" t="n">
-        <v>0.019677</v>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -16602,19 +16500,15 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Shares issued for exploration and evaluation assets 13,000,000 8,060,000 - -</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -16636,7 +16530,7 @@
         </is>
       </c>
       <c r="I189" s="5" t="n">
-        <v>0.011545</v>
+        <v>8.06</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -16667,19 +16561,15 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Professional fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Shares issued as finder’s fee 625,000 468,750 - -</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -16695,11 +16585,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H190" s="5" t="n">
-        <v>0.09420199999999999</v>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I190" s="5" t="n">
-        <v>0.138571</v>
+        <v>0.46875</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -16730,12 +16622,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Regulatory costs</t>
+          <t>Stock option exercises 225,000 30,000 - -</t>
         </is>
       </c>
       <c r="D191" t="inlineStr"/>
@@ -16754,11 +16646,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H191" s="5" t="n">
-        <v>0.018341</v>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I191" s="5" t="n">
-        <v>0.102004</v>
+        <v>0.03</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -16789,12 +16683,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Loss from debt settlement (Note 7)</t>
+          <t>Fair value of stock options exercised - 22,100 (22,100) -</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -16813,8 +16707,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H192" s="5" t="n">
-        <v>-0.3564</v>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -16848,10 +16744,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr"/>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+        </is>
+      </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>August 31, 2019 11,750,000 $ 817,264 $ 110,100 $</t>
+          <t>Warrants exercised 5,940,099 990,230 - -</t>
         </is>
       </c>
       <c r="D193" t="inlineStr"/>
@@ -16870,11 +16770,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H193" s="5" t="n">
-        <v>0.233227</v>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I193" s="5" t="n">
-        <v>-0.694137</v>
+        <v>0.9902300000000001</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -16903,10 +16805,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr"/>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+        </is>
+      </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Private placement 12,000,000 900,000 -</t>
+          <t>Fair value of warrants exercised - 23,571 (23,571) -</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -16925,8 +16831,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H194" s="5" t="n">
-        <v>0.9</v>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -16960,10 +16868,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr"/>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+        </is>
+      </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (25,947) -</t>
+          <t>Share-based compensation - - 394,666 -</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
@@ -16982,13 +16894,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>-0.025947</v>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" s="5" t="n">
+        <v>0.394666</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -17017,10 +16929,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B196" t="inlineStr"/>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+        </is>
+      </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement 1,980,000 594,000 -</t>
+          <t>Share-based compensation - - 53,183</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
@@ -17039,13 +16955,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H196" s="5" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I196" s="5" t="n">
+        <v>0.053183</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -17074,13 +16990,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr"/>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>shares           capital            reserve           surplus                Deficit             equity</t>
+        </is>
+      </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 249,960</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -17096,18 +17020,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H197" s="5" t="n">
-        <v>0.24996</v>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I197" s="5" t="n">
+        <v>-0.411632</v>
+      </c>
+      <c r="J197" s="5" t="n">
+        <v>-0.411632</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
@@ -17131,17 +17053,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B198" t="inlineStr"/>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Accounting and administrative (Note 8) $</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -17158,10 +17080,10 @@
         </is>
       </c>
       <c r="H198" s="5" t="n">
-        <v>-1.143187</v>
+        <v>0.03485</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>-1.143187</v>
+        <v>0.004113</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -17190,10 +17112,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr"/>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>August 31, 2020 25,730,000 $ 2,285,317 $ 360,060 $</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -17202,21 +17128,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F199" s="5" t="n">
+        <v>0.0055</v>
+      </c>
+      <c r="G199" s="5" t="n">
+        <v>0.02975</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>0.808053</v>
+        <v>0.01164</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>-1.837324</v>
+        <v>0.019677</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -17245,13 +17167,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Private placement 10,510,000 3,153,000 -</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -17267,13 +17197,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H200" s="5" t="n">
-        <v>3.153</v>
-      </c>
-      <c r="I200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I200" s="5" t="n">
+        <v>0.011545</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -17302,13 +17232,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr"/>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (277,904) -</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
+          <t>Professional fees (Note 8)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -17325,12 +17263,10 @@
         </is>
       </c>
       <c r="H201" s="5" t="n">
-        <v>-0.277904</v>
-      </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09420199999999999</v>
+      </c>
+      <c r="I201" s="5" t="n">
+        <v>0.138571</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
@@ -17359,10 +17295,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr"/>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Share issuance costs - warrants - (270,529) 270,529</t>
+          <t>Regulatory costs</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -17371,25 +17311,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F202" s="5" t="n">
+        <v>0.003741</v>
+      </c>
+      <c r="G202" s="5" t="n">
+        <v>0.008607999999999999</v>
+      </c>
+      <c r="H202" s="5" t="n">
+        <v>0.018341</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.102004</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -17418,10 +17350,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr"/>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Private placement - flow through shares 6,666,666 2,000,000 -</t>
+          <t>Loss from debt settlement (Note 7)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr"/>
@@ -17441,7 +17377,7 @@
         </is>
       </c>
       <c r="H203" s="5" t="n">
-        <v>2</v>
+        <v>-0.3564</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
@@ -17478,7 +17414,7 @@
       <c r="B204" t="inlineStr"/>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Share issuance costs - cash - (422,304) -</t>
+          <t>August 31, 2019 11,750,000 $ 817,264 $ 110,100 $</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -17498,12 +17434,10 @@
         </is>
       </c>
       <c r="H204" s="5" t="n">
-        <v>-0.422304</v>
-      </c>
-      <c r="I204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.233227</v>
+      </c>
+      <c r="I204" s="5" t="n">
+        <v>-0.694137</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -17535,7 +17469,7 @@
       <c r="B205" t="inlineStr"/>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Share issuance costs - warrants - (216,127) 216,127</t>
+          <t>Private placement 12,000,000 900,000 -</t>
         </is>
       </c>
       <c r="D205" t="inlineStr"/>
@@ -17554,10 +17488,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H205" s="5" t="n">
+        <v>0.9</v>
       </c>
       <c r="I205" t="inlineStr">
         <is>
@@ -17594,7 +17526,7 @@
       <c r="B206" t="inlineStr"/>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Shares issued for exploration and evaluation assets 13,000,000 8,060,000 -</t>
+          <t>Share issuance costs - cash - (25,947) -</t>
         </is>
       </c>
       <c r="D206" t="inlineStr"/>
@@ -17614,7 +17546,7 @@
         </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>8.06</v>
+        <v>-0.025947</v>
       </c>
       <c r="I206" t="inlineStr">
         <is>
@@ -17651,7 +17583,7 @@
       <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Shares issued as finder’s fee 625,000 468,750 -</t>
+          <t>Shares issued for debt settlement 1,980,000 594,000 -</t>
         </is>
       </c>
       <c r="D207" t="inlineStr"/>
@@ -17671,7 +17603,7 @@
         </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>0.46875</v>
+        <v>0.594</v>
       </c>
       <c r="I207" t="inlineStr">
         <is>
@@ -17708,7 +17640,7 @@
       <c r="B208" t="inlineStr"/>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Stock option exercises 225,000 30,000 -</t>
+          <t>Share-based compensation - - 249,960</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -17728,7 +17660,7 @@
         </is>
       </c>
       <c r="H208" s="5" t="n">
-        <v>0.03</v>
+        <v>0.24996</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
@@ -17765,10 +17697,14 @@
       <c r="B209" t="inlineStr"/>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Fair value of stock options exercised - 22,100 (22,100)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -17784,15 +17720,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>-1.143187</v>
+      </c>
+      <c r="I209" s="5" t="n">
+        <v>-1.143187</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -17824,7 +17756,7 @@
       <c r="B210" t="inlineStr"/>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Warrants exercised 5,940,099 990,230 -</t>
+          <t>August 31, 2020 25,730,000 $ 2,285,317 $ 360,060 $</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -17844,12 +17776,10 @@
         </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.9902300000000001</v>
-      </c>
-      <c r="I210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.808053</v>
+      </c>
+      <c r="I210" s="5" t="n">
+        <v>-1.837324</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -17881,7 +17811,7 @@
       <c r="B211" t="inlineStr"/>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Fair value of warrants exercised - 23,571 (23,571)</t>
+          <t>Private placement 10,510,000 3,153,000 -</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -17900,10 +17830,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H211" s="5" t="n">
+        <v>3.153</v>
       </c>
       <c r="I211" t="inlineStr">
         <is>
@@ -17940,7 +17868,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 394,666</t>
+          <t>Share issuance costs - cash - (277,904) -</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -17960,7 +17888,7 @@
         </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>0.394666</v>
+        <v>-0.277904</v>
       </c>
       <c r="I212" t="inlineStr">
         <is>
@@ -17997,14 +17925,10 @@
       <c r="B213" t="inlineStr"/>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the period - - -</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - warrants - (270,529) 270,529</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -18020,11 +17944,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" s="5" t="n">
-        <v>-2.217425</v>
-      </c>
-      <c r="I213" s="5" t="n">
-        <v>-2.217425</v>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -18056,7 +17984,7 @@
       <c r="B214" t="inlineStr"/>
       <c r="C214" t="inlineStr">
         <is>
-          <t>August 31, 2021 62,696,765 $ 15,846,104 $ 1,195,711 $</t>
+          <t>Private placement - flow through shares 6,666,666 2,000,000 -</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -18076,10 +18004,12 @@
         </is>
       </c>
       <c r="H214" s="5" t="n">
-        <v>12.987066</v>
-      </c>
-      <c r="I214" s="5" t="n">
-        <v>-4.054749</v>
+        <v>2</v>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -18111,25 +18041,27 @@
       <c r="B215" t="inlineStr"/>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2017 to August</t>
+          <t>Share issuance costs - cash - (422,304) -</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
-      <c r="E215" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="F215" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>-0.422304</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -18163,14 +18095,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B216" t="inlineStr"/>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Accounting and administration</t>
+          <t>Share issuance costs - warrants - (216,127) 216,127</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -18179,8 +18107,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F216" s="5" t="n">
-        <v>0.014796</v>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -18224,32 +18154,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B217" t="inlineStr"/>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Audit</t>
+          <t>Shares issued for exploration and evaluation assets 13,000,000 8,060,000 -</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
-      <c r="E217" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>0.0055</v>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>8.06</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -18283,38 +18211,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B218" t="inlineStr"/>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bank charges</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Shares issued as finder’s fee 625,000 468,750 -</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F218" s="5" t="n">
-        <v>0.000203</v>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>0.46875</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -18348,14 +18268,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Corporate finance fee</t>
+          <t>Stock option exercises 225,000 30,000 -</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -18364,18 +18280,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F219" s="5" t="n">
-        <v>0.025</v>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>0.03</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -18409,14 +18325,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Executive compensation (Note 7)</t>
+          <t>Fair value of stock options exercised - 22,100 (22,100)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr"/>
@@ -18425,8 +18337,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F220" s="5" t="n">
-        <v>0.021</v>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -18470,14 +18384,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B221" t="inlineStr"/>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Sponsorship</t>
+          <t>Warrants exercised 5,940,099 990,230 -</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -18486,18 +18396,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F221" s="5" t="n">
-        <v>0.005</v>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>0.9902300000000001</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
@@ -18531,14 +18441,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B222" t="inlineStr"/>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Shareholder costs</t>
+          <t>Fair value of warrants exercised - 23,571 (23,571)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr"/>
@@ -18547,8 +18453,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F222" s="5" t="n">
-        <v>0.016163</v>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -18592,32 +18500,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B223" t="inlineStr"/>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Share-based compensation (Notes 5 and 6)</t>
+          <t>Share-based compensation - - 394,666</t>
         </is>
       </c>
       <c r="D223" t="inlineStr"/>
-      <c r="E223" s="5" t="n">
-        <v>0.1225</v>
-      </c>
-      <c r="F223" s="5" t="n">
-        <v>0.094</v>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H223" s="5" t="n">
+        <v>0.394666</v>
       </c>
       <c r="I223" t="inlineStr">
         <is>
@@ -18651,41 +18557,37 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Loss and comprehensive loss for the period - - -</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E224" s="5" t="n">
-        <v>0.0045</v>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>0.016272</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H224" s="5" t="n">
+        <v>-2.217425</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>-2.217425</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -18714,14 +18616,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B225" t="inlineStr"/>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Travel and business development</t>
+          <t>August 31, 2021 62,696,765 $ 15,846,104 $ 1,195,711 $</t>
         </is>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -18730,23 +18628,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F225" s="5" t="n">
-        <v>0.000975</v>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>12.987066</v>
+      </c>
+      <c r="I225" s="5" t="n">
+        <v>-4.054749</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -18777,25 +18673,25 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Regulatory costs</t>
+          <t>Accounting and administrative $</t>
         </is>
       </c>
       <c r="D226" t="inlineStr"/>
-      <c r="E226" s="5" t="n">
-        <v>0.000191</v>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F226" s="5" t="n">
-        <v>0.008822999999999999</v>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.014796</v>
+      </c>
+      <c r="G226" s="5" t="n">
+        <v>0.024808</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -18836,29 +18732,31 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Amortization (Note 4)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E227" s="5" t="n">
-        <v>0.127219</v>
-      </c>
-      <c r="F227" s="5" t="n">
-        <v>0.207732</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" s="5" t="n">
+        <v>0.001839</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -18899,17 +18797,17 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Bank charges</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -18918,12 +18816,10 @@
         </is>
       </c>
       <c r="F228" s="5" t="n">
-        <v>-0.005583</v>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000203</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.000187</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -18964,27 +18860,29 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Other – write-down of exploration and evaluation asset (Note 4)</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
+          <t>Consulting (Note 7)</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F229" s="5" t="n">
-        <v>-0.172646</v>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025</v>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>0.0285</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -19025,25 +18923,25 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year - period</t>
+          <t>Executive compensation (Note 7)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr"/>
-      <c r="E230" s="5" t="n">
-        <v>-0.127219</v>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F230" s="5" t="n">
-        <v>-0.374795</v>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>0.022</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -19084,29 +18982,29 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Loss per share, basic and diluted</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="n">
-        <v>-2e-07</v>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F231" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01058</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>0.019442</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -19147,29 +19045,25 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E232" s="5" t="n">
-        <v>0.627885</v>
+          <t>Share-based compensation (Note 7)</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F232" s="5" t="n">
-        <v>9.037789</v>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.094</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>0.0161</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -19210,20 +19104,22 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Meridius Resources Limited.</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Meridius Resources Limited. ended August 31, 2018 and period July</t>
+          <t>Sponsorship</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
-      <c r="E233" s="5" t="n">
-        <v>0.002017</v>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F233" s="5" t="n">
-        <v>1e-05</v>
+        <v>0.005</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -19269,29 +19165,29 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>shares                                                          deficit                 Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Balance at July 10, 2017 - - -</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Transfer agent</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F234" s="5" t="n">
+        <v>0.005082</v>
+      </c>
+      <c r="G234" s="5" t="n">
+        <v>0.007723</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -19332,22 +19228,22 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>shares                                                          deficit                 Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Common shares issued for private placement 5,050,000 252,500 -</t>
+          <t>Write-down of exploration and evaluation asset</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" s="5" t="n">
-        <v>0.2525</v>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.172646</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -19393,12 +19289,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>shares                                                          deficit                 Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Net income (loss) for the period - - -</t>
+          <t>Comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -19406,16 +19302,16 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E236" s="5" t="n">
-        <v>-0.127219</v>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F236" s="5" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.374795</v>
+      </c>
+      <c r="G236" s="5" t="n">
+        <v>-0.192123</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -19456,25 +19352,29 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>shares                                                          deficit                 Equity</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Balance at August 31, 2017 5,050,000 252,500 -</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
-      <c r="E237" s="5" t="n">
-        <v>-0.125281</v>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F237" s="5" t="n">
-        <v>-0.127219</v>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.037789</v>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>11.75</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -19513,24 +19413,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Common shares issued for:                                                                                                                           -</t>
-        </is>
-      </c>
+      <c r="B238" t="inlineStr"/>
       <c r="C238" t="inlineStr">
         <is>
-          <t>- Initial public offering 6,500,000 650,000 -</t>
+          <t>2017 to August</t>
         </is>
       </c>
       <c r="D238" t="inlineStr"/>
       <c r="E238" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="F238" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -19576,22 +19470,22 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Common shares issued for:                                                                                                                           -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>- Evaluation asset option 200,000 20,000 -</t>
+          <t>Accounting and administration</t>
         </is>
       </c>
       <c r="D239" t="inlineStr"/>
-      <c r="E239" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F239" s="5" t="n">
+        <v>0.014796</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -19637,20 +19531,20 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Common shares issued for:                                                                                                                           -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
+          <t>Audit</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
       <c r="E240" s="5" t="n">
-        <v>-0.105236</v>
+        <v>2.8e-05</v>
       </c>
       <c r="F240" s="5" t="n">
-        <v>-0.105236</v>
+        <v>0.0055</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -19696,22 +19590,26 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Common shares issued for:                                                                                                                           -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 94,000</t>
-        </is>
-      </c>
-      <c r="D241" t="inlineStr"/>
-      <c r="E241" s="5" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F241" s="5" t="n">
+        <v>0.000203</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -19757,24 +19655,22 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Common shares issued for:                                                                                                                           -</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Net income (loss) for the period - - -</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E242" s="5" t="n">
-        <v>-0.374795</v>
+          <t>Corporate finance fee</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F242" s="5" t="n">
-        <v>-0.374795</v>
+        <v>0.025</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -19820,52 +19716,1461 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Executive compensation (Note 7)</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F243" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Sponsorship</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Shareholder costs</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F245" s="5" t="n">
+        <v>0.016163</v>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Share-based compensation (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" s="5" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="F246" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="F247" s="5" t="n">
+        <v>0.016272</v>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Travel and business development</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F248" s="5" t="n">
+        <v>0.000975</v>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Regulatory costs</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" s="5" t="n">
+        <v>0.000191</v>
+      </c>
+      <c r="F249" s="5" t="n">
+        <v>0.008822999999999999</v>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="n">
+        <v>0.127219</v>
+      </c>
+      <c r="F250" s="5" t="n">
+        <v>0.207732</v>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>-0.005583</v>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Other – write-down of exploration and evaluation asset (Note 4)</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" s="5" t="n">
+        <v>-0.172646</v>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the year - period</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" s="5" t="n">
+        <v>-0.127219</v>
+      </c>
+      <c r="F253" s="5" t="n">
+        <v>-0.374795</v>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Loss per share, basic and diluted</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="n">
+        <v>-2e-07</v>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="n">
+        <v>0.627885</v>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>9.037789</v>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Meridius Resources Limited.</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Meridius Resources Limited. ended August 31, 2018 and period July</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>shares                                                          deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Balance at July 10, 2017 - - -</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>shares                                                          deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Common shares issued for private placement 5,050,000 252,500 -</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" s="5" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>shares                                                          deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the period - - -</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="n">
+        <v>-0.127219</v>
+      </c>
+      <c r="F259" s="5" t="n">
+        <v>-0.127219</v>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>shares                                                          deficit                 Equity</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Balance at August 31, 2017 5,050,000 252,500 -</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" s="5" t="n">
+        <v>-0.125281</v>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>-0.127219</v>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
           <t>Common shares issued for:                                                                                                                           -</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr">
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>- Initial public offering 6,500,000 650,000 -</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" s="5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Common shares issued for:                                                                                                                           -</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>- Evaluation asset option 200,000 20,000 -</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Common shares issued for:                                                                                                                           -</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Share issue costs</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" s="5" t="n">
+        <v>-0.105236</v>
+      </c>
+      <c r="F263" s="5" t="n">
+        <v>-0.105236</v>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Common shares issued for:                                                                                                                           -</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Share-based compensation - - 94,000</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Common shares issued for:                                                                                                                           -</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Net income (loss) for the period - - -</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="n">
+        <v>-0.374795</v>
+      </c>
+      <c r="F265" s="5" t="n">
+        <v>-0.374795</v>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Common shares issued for:                                                                                                                           -</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
         <is>
           <t>Balance at August 31, 2018 11,750,000 817,264 94,000</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" s="5" t="n">
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" s="5" t="n">
         <v>-0.40925</v>
       </c>
-      <c r="F243" s="5" t="n">
+      <c r="F266" s="5" t="n">
         <v>-0.502014</v>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M243" t="inlineStr">
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
         <is>
           <t>-</t>
         </is>
